--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97958</v>
+        <v>97963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96571</v>
+        <v>96576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96571</v>
+        <v>96576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92517</v>
+        <v>92522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136734779</v>
       </c>
       <c r="B21" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81132</v>
+        <v>81134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>136724447</v>
       </c>
       <c r="B26" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136734880</v>
       </c>
       <c r="B27" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>136724645</v>
       </c>
       <c r="B28" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>136726966</v>
       </c>
       <c r="B29" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>136728315</v>
       </c>
       <c r="B33" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99683</v>
+        <v>99688</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99655</v>
+        <v>99660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97963</v>
+        <v>97965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96576</v>
+        <v>96578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96576</v>
+        <v>96578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99688</v>
+        <v>99690</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4610,37 +4610,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136731586</v>
+        <v>136726098</v>
       </c>
       <c r="B38" t="n">
-        <v>99351</v>
+        <v>106494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åtvid, Sm</t>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>573144</v>
+        <v>573147</v>
       </c>
       <c r="R38" t="n">
-        <v>6452957</v>
+        <v>6452953</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,74 +4714,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136731586</t>
+          <t>https://artportalen.se/Sighting/136726098</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136731587</v>
+        <v>136724691</v>
       </c>
       <c r="B39" t="n">
-        <v>99351</v>
+        <v>106369</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221154</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åtvid, Sm</t>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573141</v>
+        <v>573129</v>
       </c>
       <c r="R39" t="n">
-        <v>6452947</v>
+        <v>6452987</v>
       </c>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4810,7 +4801,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4820,7 +4811,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4835,27 +4826,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136731587</t>
+          <t>https://artportalen.se/Sighting/136724691</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136726098</v>
+        <v>136726571</v>
       </c>
       <c r="B40" t="n">
-        <v>106492</v>
+        <v>99662</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,40 +4854,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>222857</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573147</v>
+        <v>573178</v>
       </c>
       <c r="R40" t="n">
         <v>6452953</v>
@@ -4931,7 +4913,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4941,7 +4923,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4966,230 +4948,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136726098</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>136724691</v>
-      </c>
-      <c r="B41" t="n">
-        <v>106367</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221154</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skogsstjärna</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lysimachia europaea</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>573129</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6452987</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Hannäs</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136724691</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>136726571</v>
-      </c>
-      <c r="B42" t="n">
-        <v>99660</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>222857</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ekorrbär</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Maianthemum bifolium</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(L.) F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>573178</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6452953</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Hannäs</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136726571</t>
         </is>
@@ -5236,8 +4994,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4610,37 +4610,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136726098</v>
+        <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>106494</v>
+        <v>99353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+          <t>Åtvid, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>573147</v>
+        <v>573144</v>
       </c>
       <c r="R38" t="n">
-        <v>6452953</v>
+        <v>6452957</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,65 +4714,74 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136726098</t>
+          <t>https://artportalen.se/Sighting/136731586</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136724691</v>
+        <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>106369</v>
+        <v>99353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221154</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+          <t>Åtvid, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573129</v>
+        <v>573141</v>
       </c>
       <c r="R39" t="n">
-        <v>6452987</v>
+        <v>6452947</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4801,7 +4810,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4811,7 +4820,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4826,27 +4835,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136724691</t>
+          <t>https://artportalen.se/Sighting/136731587</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136726571</v>
+        <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>99662</v>
+        <v>106494</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4854,31 +4863,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222857</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573178</v>
+        <v>573147</v>
       </c>
       <c r="R40" t="n">
         <v>6452953</v>
@@ -4913,7 +4931,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4923,7 +4941,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4948,6 +4966,230 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136726098</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136724691</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106369</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>573129</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6452987</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136724691</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136726571</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99662</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>573178</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6452953</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136726571</t>
         </is>
@@ -4994,6 +5236,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96656</v>
+        <v>96662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96578</v>
+        <v>96584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96578</v>
+        <v>96584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81134</v>
+        <v>81138</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99690</v>
+        <v>99696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4610,37 +4610,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136731586</v>
+        <v>136726098</v>
       </c>
       <c r="B38" t="n">
-        <v>99353</v>
+        <v>106500</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åtvid, Sm</t>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>573144</v>
+        <v>573147</v>
       </c>
       <c r="R38" t="n">
-        <v>6452957</v>
+        <v>6452953</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,74 +4714,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136731586</t>
+          <t>https://artportalen.se/Sighting/136726098</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136731587</v>
+        <v>136724691</v>
       </c>
       <c r="B39" t="n">
-        <v>99353</v>
+        <v>106375</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221154</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åtvid, Sm</t>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573141</v>
+        <v>573129</v>
       </c>
       <c r="R39" t="n">
-        <v>6452947</v>
+        <v>6452987</v>
       </c>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4810,7 +4801,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4820,7 +4811,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4835,27 +4826,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136731587</t>
+          <t>https://artportalen.se/Sighting/136724691</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136726098</v>
+        <v>136726571</v>
       </c>
       <c r="B40" t="n">
-        <v>106494</v>
+        <v>99668</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,40 +4854,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>222857</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573147</v>
+        <v>573178</v>
       </c>
       <c r="R40" t="n">
         <v>6452953</v>
@@ -4931,7 +4913,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4941,7 +4923,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4966,230 +4948,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136726098</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>136724691</v>
-      </c>
-      <c r="B41" t="n">
-        <v>106369</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221154</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skogsstjärna</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lysimachia europaea</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>573129</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6452987</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Hannäs</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136724691</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>136726571</v>
-      </c>
-      <c r="B42" t="n">
-        <v>99662</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>222857</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ekorrbär</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Maianthemum bifolium</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(L.) F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>573178</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6452953</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Hannäs</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136726571</t>
         </is>
@@ -5236,8 +4994,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96662</v>
+        <v>96664</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81138</v>
+        <v>81140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99696</v>
+        <v>99698</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4610,37 +4610,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136726098</v>
+        <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>106500</v>
+        <v>99361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+          <t>Åtvid, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>573147</v>
+        <v>573144</v>
       </c>
       <c r="R38" t="n">
-        <v>6452953</v>
+        <v>6452957</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,65 +4714,74 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136726098</t>
+          <t>https://artportalen.se/Sighting/136731586</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136724691</v>
+        <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>106375</v>
+        <v>99361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221154</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+          <t>Åtvid, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573129</v>
+        <v>573141</v>
       </c>
       <c r="R39" t="n">
-        <v>6452987</v>
+        <v>6452947</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4801,7 +4810,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4811,7 +4820,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4826,27 +4835,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136724691</t>
+          <t>https://artportalen.se/Sighting/136731587</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136726571</v>
+        <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>99668</v>
+        <v>106502</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4854,31 +4863,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222857</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573178</v>
+        <v>573147</v>
       </c>
       <c r="R40" t="n">
         <v>6452953</v>
@@ -4913,7 +4931,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4923,7 +4941,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4948,6 +4966,230 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136726098</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136724691</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106377</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>573129</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6452987</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136724691</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136726571</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99670</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>573178</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6452953</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136726571</t>
         </is>
@@ -4994,6 +5236,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4610,37 +4610,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136731586</v>
+        <v>136726098</v>
       </c>
       <c r="B38" t="n">
-        <v>99361</v>
+        <v>106502</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åtvid, Sm</t>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>573144</v>
+        <v>573147</v>
       </c>
       <c r="R38" t="n">
-        <v>6452957</v>
+        <v>6452953</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,74 +4714,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136731586</t>
+          <t>https://artportalen.se/Sighting/136726098</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136731587</v>
+        <v>136724691</v>
       </c>
       <c r="B39" t="n">
-        <v>99361</v>
+        <v>106377</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221154</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åtvid, Sm</t>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573141</v>
+        <v>573129</v>
       </c>
       <c r="R39" t="n">
-        <v>6452947</v>
+        <v>6452987</v>
       </c>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4810,7 +4801,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4820,7 +4811,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4835,27 +4826,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elinne Lotz</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136731587</t>
+          <t>https://artportalen.se/Sighting/136724691</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136726098</v>
+        <v>136726571</v>
       </c>
       <c r="B40" t="n">
-        <v>106502</v>
+        <v>99670</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,40 +4854,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>222857</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573147</v>
+        <v>573178</v>
       </c>
       <c r="R40" t="n">
         <v>6452953</v>
@@ -4931,7 +4913,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4941,7 +4923,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4966,230 +4948,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136726098</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>136724691</v>
-      </c>
-      <c r="B41" t="n">
-        <v>106377</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221154</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skogsstjärna</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lysimachia europaea</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>573129</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6452987</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Hannäs</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136724691</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>136726571</v>
-      </c>
-      <c r="B42" t="n">
-        <v>99670</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>222857</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ekorrbär</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Maianthemum bifolium</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(L.) F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>573178</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6452953</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Hannäs</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Johan Holmgren</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136726571</t>
         </is>
@@ -5236,8 +4994,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96664</v>
+        <v>96665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96586</v>
+        <v>96587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96586</v>
+        <v>96587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81140</v>
+        <v>81141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99698</v>
+        <v>99699</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136726098</v>
       </c>
       <c r="B38" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136724691</v>
       </c>
       <c r="B39" t="n">
-        <v>106377</v>
+        <v>106378</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>136726571</v>
       </c>
       <c r="B40" t="n">
-        <v>99670</v>
+        <v>99671</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4610,37 +4610,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136726098</v>
+        <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>106503</v>
+        <v>99362</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+          <t>Åtvid, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>573147</v>
+        <v>573144</v>
       </c>
       <c r="R38" t="n">
-        <v>6452953</v>
+        <v>6452957</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,65 +4714,74 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136726098</t>
+          <t>https://artportalen.se/Sighting/136731586</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136724691</v>
+        <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>106378</v>
+        <v>99362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221154</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+          <t>Åtvid, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573129</v>
+        <v>573141</v>
       </c>
       <c r="R39" t="n">
-        <v>6452987</v>
+        <v>6452947</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4801,7 +4810,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4811,7 +4820,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4826,27 +4835,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136724691</t>
+          <t>https://artportalen.se/Sighting/136731587</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136726571</v>
+        <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>99671</v>
+        <v>106503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4854,31 +4863,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222857</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hagståndsberget, Hagståndsberget, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573178</v>
+        <v>573147</v>
       </c>
       <c r="R40" t="n">
         <v>6452953</v>
@@ -4913,7 +4931,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4923,7 +4941,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4948,6 +4966,230 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136726098</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136724691</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106378</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>573129</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6452987</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136724691</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136726571</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99671</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hagståndsberget, Hagståndsberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>573178</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6452953</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136726571</t>
         </is>
@@ -4994,6 +5236,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96665</v>
+        <v>96671</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96587</v>
+        <v>96593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96587</v>
+        <v>96593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99699</v>
+        <v>99705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106378</v>
+        <v>106384</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99671</v>
+        <v>99677</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96671</v>
+        <v>96675</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96593</v>
+        <v>96597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96593</v>
+        <v>96597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81141</v>
+        <v>81143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99705</v>
+        <v>99709</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106384</v>
+        <v>106388</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99677</v>
+        <v>99681</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96597</v>
+        <v>96599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96597</v>
+        <v>96599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99709</v>
+        <v>99711</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106388</v>
+        <v>106390</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99681</v>
+        <v>99683</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96677</v>
+        <v>96679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81143</v>
+        <v>81146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99711</v>
+        <v>99713</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106390</v>
+        <v>106392</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99683</v>
+        <v>99685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96679</v>
+        <v>96692</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136734779</v>
       </c>
       <c r="B21" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81146</v>
+        <v>81159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>136724447</v>
       </c>
       <c r="B26" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136734880</v>
       </c>
       <c r="B27" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>136724645</v>
       </c>
       <c r="B28" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>136726966</v>
       </c>
       <c r="B29" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>136728315</v>
       </c>
       <c r="B33" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99713</v>
+        <v>99726</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106392</v>
+        <v>106405</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99685</v>
+        <v>99698</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136734779</v>
       </c>
       <c r="B21" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81159</v>
+        <v>81161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>136724447</v>
       </c>
       <c r="B26" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136734880</v>
       </c>
       <c r="B27" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>136724645</v>
       </c>
       <c r="B28" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>136726966</v>
       </c>
       <c r="B29" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>136734724</v>
       </c>
       <c r="B31" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>136725458</v>
       </c>
       <c r="B32" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>136728315</v>
       </c>
       <c r="B33" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99726</v>
+        <v>99728</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106405</v>
+        <v>106407</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99698</v>
+        <v>99700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -3298,11 +3298,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hagståndsberget, Hagståndsberget, Sm</t>
@@ -3417,11 +3413,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3527,11 +3519,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3637,11 +3625,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3748,11 +3732,7 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3860,11 +3840,7 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3972,11 +3948,7 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99728</v>
+        <v>99731</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106407</v>
+        <v>106411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99700</v>
+        <v>99703</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136734779</v>
       </c>
       <c r="B21" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136725345</v>
       </c>
       <c r="B22" t="n">
-        <v>81161</v>
+        <v>81171</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136724598</v>
       </c>
       <c r="B23" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136724949</v>
       </c>
       <c r="B24" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136725211</v>
       </c>
       <c r="B25" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>136724447</v>
       </c>
       <c r="B26" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>136734880</v>
       </c>
       <c r="B27" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136724645</v>
       </c>
       <c r="B28" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136726966</v>
       </c>
       <c r="B29" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>136734838</v>
       </c>
       <c r="B30" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>136734724</v>
       </c>
       <c r="B31" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136725458</v>
       </c>
       <c r="B32" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>136728315</v>
       </c>
       <c r="B33" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99731</v>
+        <v>99741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106411</v>
+        <v>106430</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99703</v>
+        <v>99713</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136734767</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136731594</v>
       </c>
       <c r="B3" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136726215</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136723438</v>
       </c>
       <c r="B5" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136724383</v>
       </c>
       <c r="B6" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136724400</v>
       </c>
       <c r="B7" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136725336</v>
       </c>
       <c r="B8" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136725973</v>
       </c>
       <c r="B9" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136734844</v>
       </c>
       <c r="B10" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136725259</v>
       </c>
       <c r="B11" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136725462</v>
       </c>
       <c r="B12" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136726811</v>
       </c>
       <c r="B13" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136724248</v>
       </c>
       <c r="B14" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136725015</v>
       </c>
       <c r="B15" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>136727302</v>
       </c>
       <c r="B16" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>136734758</v>
       </c>
       <c r="B17" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>136727068</v>
       </c>
       <c r="B18" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136727997</v>
       </c>
       <c r="B19" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136728037</v>
       </c>
       <c r="B20" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>136725020</v>
       </c>
       <c r="B34" t="n">
-        <v>99741</v>
+        <v>99742</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136728259</v>
       </c>
       <c r="B35" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136726363</v>
       </c>
       <c r="B36" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>136728054</v>
       </c>
       <c r="B37" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>136726098</v>
       </c>
       <c r="B40" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>136724691</v>
       </c>
       <c r="B41" t="n">
-        <v>106430</v>
+        <v>106431</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>136726571</v>
       </c>
       <c r="B42" t="n">
-        <v>99713</v>
+        <v>99714</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -4585,7 +4585,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 37636-2026 artfynd.xlsx
+++ b/artfynd/A 37636-2026 artfynd.xlsx
@@ -4585,7 +4585,7 @@
         <v>136731586</v>
       </c>
       <c r="B38" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>136731587</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
